--- a/terminology/ValueSet-cz-sitequalifier.xlsx
+++ b/terminology/ValueSet-cz-sitequalifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -108,151 +108,76 @@
     <t>7771000</t>
   </si>
   <si>
-    <t>levý</t>
-  </si>
-  <si>
     <t>24028007</t>
   </si>
   <si>
-    <t>pravý</t>
-  </si>
-  <si>
     <t>51440002</t>
   </si>
   <si>
-    <t>laterálně</t>
-  </si>
-  <si>
     <t>46053002</t>
   </si>
   <si>
-    <t>distálně</t>
-  </si>
-  <si>
     <t>255554000</t>
   </si>
   <si>
-    <t>dorzálně</t>
-  </si>
-  <si>
     <t>261183002</t>
   </si>
   <si>
-    <t>horní</t>
-  </si>
-  <si>
     <t>261122009</t>
   </si>
   <si>
-    <t>dolní</t>
-  </si>
-  <si>
     <t>255561001</t>
   </si>
   <si>
-    <t>mediální</t>
-  </si>
-  <si>
     <t>49370004</t>
   </si>
   <si>
-    <t>laterální</t>
-  </si>
-  <si>
     <t>264217000</t>
   </si>
   <si>
-    <t>superioriní</t>
-  </si>
-  <si>
     <t>261089000</t>
   </si>
   <si>
-    <t>inferiorní</t>
-  </si>
-  <si>
     <t>255551008</t>
   </si>
   <si>
-    <t>posteriorní</t>
-  </si>
-  <si>
     <t>351726001</t>
   </si>
   <si>
-    <t>pod</t>
-  </si>
-  <si>
     <t>352730000</t>
   </si>
   <si>
-    <t>nad</t>
-  </si>
-  <si>
     <t>40415009</t>
   </si>
   <si>
-    <t>proximální</t>
-  </si>
-  <si>
     <t>255549009</t>
   </si>
   <si>
-    <t>anteriorní</t>
-  </si>
-  <si>
     <t>26283006</t>
   </si>
   <si>
-    <t>povrchový</t>
-  </si>
-  <si>
     <t>795002</t>
   </si>
   <si>
-    <t>hloboký</t>
-  </si>
-  <si>
     <t>57195005</t>
   </si>
   <si>
-    <t>bazální</t>
-  </si>
-  <si>
     <t>3583002</t>
   </si>
   <si>
-    <t>kaudální</t>
-  </si>
-  <si>
     <t>66787007</t>
   </si>
   <si>
-    <t>cefalický</t>
-  </si>
-  <si>
     <t>255481003</t>
   </si>
   <si>
-    <t>levý horní kvadrant</t>
-  </si>
-  <si>
     <t>255497008</t>
   </si>
   <si>
-    <t>pravý horní kvadrant</t>
-  </si>
-  <si>
     <t>255480002</t>
   </si>
   <si>
-    <t>levý dolní kvadrant</t>
-  </si>
-  <si>
     <t>255495000</t>
-  </si>
-  <si>
-    <t>pravý dolní kvadrant</t>
   </si>
   <si>
     <t/>
@@ -546,216 +471,166 @@
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>39</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>41</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>43</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>47</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>49</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>51</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>53</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>55</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>59</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>63</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>67</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>69</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
